--- a/diseases/d053/2005-2009.xlsx
+++ b/diseases/d053/2005-2009.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -765,126 +765,34 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
+          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>sha256:6034eee94b5d9422fa4d3e5aa1eb74561d1707e29cb995008fef66e10c4d9593</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN2" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -897,12 +805,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -917,400 +825,10 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
-        <is>
-          <t>official_webforms_csv_export</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>D053</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>lassa</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Lassa</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DE-NW</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Nordrhein-Westfalen, Germany</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>D053</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Lassa</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>拉沙热</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2006-07-17</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2006-07</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>D053</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>lassa</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Lassa</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DE-NW</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Nordrhein-Westfalen, Germany</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>D053</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Lassa</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>拉沙热</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2006-07-17</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2006-07</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>lassafieber</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Lassafieber</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:DE-NW:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1442,7 +960,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1462,7 +980,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1472,7 +990,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d053/2005-2009.xlsx
+++ b/diseases/d053/2005-2009.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -765,34 +765,126 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>sha256:6034eee94b5d9422fa4d3e5aa1eb74561d1707e29cb995008fef66e10c4d9593</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>1</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -805,30 +897,420 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DE-NW</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen, Germany</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2006-07-17</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2006-07</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>rki_survstat</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lassa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DE-NW</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen, Germany</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>D053</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Lassa</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>拉沙热</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2006-07-17</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2006-07</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>lassafieber</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Lassafieber</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:DE-NW:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>HOLD_DE_804398280e024ae1d6e7a8302f79</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -960,7 +1442,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -980,7 +1462,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -990,7 +1472,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
